--- a/demo_output/figure_06_Danmark — Offentlig gæld (% af BNP).xlsx
+++ b/demo_output/figure_06_Danmark — Offentlig gæld (% af BNP).xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grafik" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Danmark — Offentlig gæld (% af " sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Danmark — Offentlig gæld" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -482,7 +482,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Danmark — Offentlig gæld (% af BNP)</t>
+          <t>Danmark — Offentlig gæld</t>
         </is>
       </c>
     </row>
